--- a/Datos limpios/Pricing diario/Histórico/Cebada.xlsx
+++ b/Datos limpios/Pricing diario/Histórico/Cebada.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2913"/>
+  <dimension ref="A1:K2919"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -108162,301 +108162,229 @@
         </is>
       </c>
     </row>
+    <row r="2914">
+      <c r="A2914" s="2">
+        <v>45950</v>
+      </c>
+      <c r="B2914">
+        <v>25070</v>
+      </c>
+      <c r="C2914">
+        <v>40</v>
+      </c>
+      <c r="D2914">
+        <v>0</v>
+      </c>
+      <c r="E2914">
+        <v>25110</v>
+      </c>
+      <c r="F2914">
+        <v>4340</v>
+      </c>
+      <c r="G2914">
+        <v>0</v>
+      </c>
+      <c r="H2914">
+        <v>0</v>
+      </c>
+      <c r="I2914">
+        <v>4340</v>
+      </c>
+      <c r="J2914">
+        <v>29450</v>
+      </c>
+      <c r="K2914" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="A2915" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B2915">
+        <v>32288.12</v>
+      </c>
+      <c r="C2915">
+        <v>0</v>
+      </c>
+      <c r="D2915">
+        <v>400</v>
+      </c>
+      <c r="E2915">
+        <v>31888.12</v>
+      </c>
+      <c r="F2915">
+        <v>500</v>
+      </c>
+      <c r="G2915">
+        <v>0</v>
+      </c>
+      <c r="H2915">
+        <v>0</v>
+      </c>
+      <c r="I2915">
+        <v>500</v>
+      </c>
+      <c r="J2915">
+        <v>32388.12</v>
+      </c>
+      <c r="K2915" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="A2916" s="2">
+        <v>45952</v>
+      </c>
+      <c r="B2916">
+        <v>23990.26</v>
+      </c>
+      <c r="C2916">
+        <v>4240</v>
+      </c>
+      <c r="D2916">
+        <v>0</v>
+      </c>
+      <c r="E2916">
+        <v>28230.26</v>
+      </c>
+      <c r="F2916">
+        <v>1500</v>
+      </c>
+      <c r="G2916">
+        <v>0</v>
+      </c>
+      <c r="H2916">
+        <v>0</v>
+      </c>
+      <c r="I2916">
+        <v>1500</v>
+      </c>
+      <c r="J2916">
+        <v>29730.26</v>
+      </c>
+      <c r="K2916" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="A2917" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B2917">
+        <v>10986</v>
+      </c>
+      <c r="C2917">
+        <v>500</v>
+      </c>
+      <c r="D2917">
+        <v>0</v>
+      </c>
+      <c r="E2917">
+        <v>11486</v>
+      </c>
+      <c r="F2917">
+        <v>30</v>
+      </c>
+      <c r="G2917">
+        <v>0</v>
+      </c>
+      <c r="H2917">
+        <v>0</v>
+      </c>
+      <c r="I2917">
+        <v>30</v>
+      </c>
+      <c r="J2917">
+        <v>11516</v>
+      </c>
+      <c r="K2917" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="A2918" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B2918">
+        <v>14826.67</v>
+      </c>
+      <c r="C2918">
+        <v>710</v>
+      </c>
+      <c r="D2918">
+        <v>0</v>
+      </c>
+      <c r="E2918">
+        <v>15536.67</v>
+      </c>
+      <c r="F2918">
+        <v>51.18000000000001</v>
+      </c>
+      <c r="G2918">
+        <v>0</v>
+      </c>
+      <c r="H2918">
+        <v>0</v>
+      </c>
+      <c r="I2918">
+        <v>51.18000000000001</v>
+      </c>
+      <c r="J2918">
+        <v>15587.85</v>
+      </c>
+      <c r="K2918" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="A2919" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B2919">
+        <v>450</v>
+      </c>
+      <c r="C2919">
+        <v>0</v>
+      </c>
+      <c r="D2919">
+        <v>0</v>
+      </c>
+      <c r="E2919">
+        <v>450</v>
+      </c>
+      <c r="F2919">
+        <v>7500</v>
+      </c>
+      <c r="G2919">
+        <v>0</v>
+      </c>
+      <c r="H2919">
+        <v>0</v>
+      </c>
+      <c r="I2919">
+        <v>7500</v>
+      </c>
+      <c r="J2919">
+        <v>7950</v>
+      </c>
+      <c r="K2919" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bac5de4a034fee97af64ba5a2822cd53">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="027d3429df443898fbbc0b888682b5bf" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07E2DD3B-91E7-4DED-BDAD-CEEF1380723B}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37F11506-5A93-4C75-A3E9-778DA3CF7E47}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1C83A18-11C8-47B2-B628-8E63D398AA69}"/>
 </file>
--- a/Datos limpios/Pricing diario/Histórico/Cebada.xlsx
+++ b/Datos limpios/Pricing diario/Histórico/Cebada.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2919"/>
+  <dimension ref="A1:K2938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -108352,33 +108352,736 @@
         <v>45957</v>
       </c>
       <c r="B2919">
+        <v>7856.26</v>
+      </c>
+      <c r="C2919">
+        <v>0</v>
+      </c>
+      <c r="D2919">
+        <v>0</v>
+      </c>
+      <c r="E2919">
+        <v>7856.26</v>
+      </c>
+      <c r="F2919">
+        <v>11532.08</v>
+      </c>
+      <c r="G2919">
+        <v>0</v>
+      </c>
+      <c r="H2919">
+        <v>0</v>
+      </c>
+      <c r="I2919">
+        <v>11532.08</v>
+      </c>
+      <c r="J2919">
+        <v>19388.34</v>
+      </c>
+      <c r="K2919" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2920">
+      <c r="A2920" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B2920">
+        <v>10205.26</v>
+      </c>
+      <c r="C2920">
+        <v>0</v>
+      </c>
+      <c r="D2920">
+        <v>0</v>
+      </c>
+      <c r="E2920">
+        <v>10205.26</v>
+      </c>
+      <c r="F2920">
+        <v>8016</v>
+      </c>
+      <c r="G2920">
+        <v>0</v>
+      </c>
+      <c r="H2920">
+        <v>0</v>
+      </c>
+      <c r="I2920">
+        <v>8016</v>
+      </c>
+      <c r="J2920">
+        <v>18221.26</v>
+      </c>
+      <c r="K2920" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B2921">
+        <v>10783</v>
+      </c>
+      <c r="C2921">
+        <v>1030</v>
+      </c>
+      <c r="D2921">
+        <v>340</v>
+      </c>
+      <c r="E2921">
+        <v>11473</v>
+      </c>
+      <c r="F2921">
+        <v>300</v>
+      </c>
+      <c r="G2921">
+        <v>0</v>
+      </c>
+      <c r="H2921">
+        <v>0</v>
+      </c>
+      <c r="I2921">
+        <v>300</v>
+      </c>
+      <c r="J2921">
+        <v>11773</v>
+      </c>
+      <c r="K2921" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B2922">
+        <v>18056.23</v>
+      </c>
+      <c r="C2922">
+        <v>0</v>
+      </c>
+      <c r="D2922">
+        <v>0</v>
+      </c>
+      <c r="E2922">
+        <v>18056.23</v>
+      </c>
+      <c r="F2922">
+        <v>3480</v>
+      </c>
+      <c r="G2922">
+        <v>0</v>
+      </c>
+      <c r="H2922">
+        <v>0</v>
+      </c>
+      <c r="I2922">
+        <v>3480</v>
+      </c>
+      <c r="J2922">
+        <v>21536.23</v>
+      </c>
+      <c r="K2922" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B2923">
+        <v>30580</v>
+      </c>
+      <c r="C2923">
+        <v>0</v>
+      </c>
+      <c r="D2923">
+        <v>150</v>
+      </c>
+      <c r="E2923">
+        <v>30430</v>
+      </c>
+      <c r="F2923">
+        <v>930</v>
+      </c>
+      <c r="G2923">
+        <v>0</v>
+      </c>
+      <c r="H2923">
+        <v>0</v>
+      </c>
+      <c r="I2923">
+        <v>930</v>
+      </c>
+      <c r="J2923">
+        <v>31360</v>
+      </c>
+      <c r="K2923" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B2924">
+        <v>26005.8</v>
+      </c>
+      <c r="C2924">
+        <v>0</v>
+      </c>
+      <c r="D2924">
+        <v>0</v>
+      </c>
+      <c r="E2924">
+        <v>26005.8</v>
+      </c>
+      <c r="F2924">
         <v>450</v>
       </c>
-      <c r="C2919">
-        <v>0</v>
-      </c>
-      <c r="D2919">
-        <v>0</v>
-      </c>
-      <c r="E2919">
+      <c r="G2924">
+        <v>0</v>
+      </c>
+      <c r="H2924">
+        <v>0</v>
+      </c>
+      <c r="I2924">
         <v>450</v>
       </c>
-      <c r="F2919">
-        <v>7500</v>
-      </c>
-      <c r="G2919">
-        <v>0</v>
-      </c>
-      <c r="H2919">
-        <v>0</v>
-      </c>
-      <c r="I2919">
-        <v>7500</v>
-      </c>
-      <c r="J2919">
-        <v>7950</v>
-      </c>
-      <c r="K2919" t="inlineStr">
+      <c r="J2924">
+        <v>26455.8</v>
+      </c>
+      <c r="K2924" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B2925">
+        <v>8770</v>
+      </c>
+      <c r="C2925">
+        <v>0</v>
+      </c>
+      <c r="D2925">
+        <v>0</v>
+      </c>
+      <c r="E2925">
+        <v>8770</v>
+      </c>
+      <c r="F2925">
+        <v>32590.76</v>
+      </c>
+      <c r="G2925">
+        <v>0</v>
+      </c>
+      <c r="H2925">
+        <v>0</v>
+      </c>
+      <c r="I2925">
+        <v>32590.76</v>
+      </c>
+      <c r="J2925">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="K2925" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B2926">
+        <v>20645.77</v>
+      </c>
+      <c r="C2926">
+        <v>0</v>
+      </c>
+      <c r="D2926">
+        <v>0</v>
+      </c>
+      <c r="E2926">
+        <v>20645.77</v>
+      </c>
+      <c r="F2926">
+        <v>27.88</v>
+      </c>
+      <c r="G2926">
+        <v>0</v>
+      </c>
+      <c r="H2926">
+        <v>0</v>
+      </c>
+      <c r="I2926">
+        <v>27.88</v>
+      </c>
+      <c r="J2926">
+        <v>20673.65</v>
+      </c>
+      <c r="K2926" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="A2927" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B2927">
+        <v>12972.76</v>
+      </c>
+      <c r="C2927">
+        <v>0</v>
+      </c>
+      <c r="D2927">
+        <v>2000</v>
+      </c>
+      <c r="E2927">
+        <v>10972.76</v>
+      </c>
+      <c r="F2927">
+        <v>1320</v>
+      </c>
+      <c r="G2927">
+        <v>0</v>
+      </c>
+      <c r="H2927">
+        <v>0</v>
+      </c>
+      <c r="I2927">
+        <v>1320</v>
+      </c>
+      <c r="J2927">
+        <v>12292.76</v>
+      </c>
+      <c r="K2927" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B2928">
+        <v>16406.74</v>
+      </c>
+      <c r="C2928">
+        <v>0</v>
+      </c>
+      <c r="D2928">
+        <v>0</v>
+      </c>
+      <c r="E2928">
+        <v>16406.74</v>
+      </c>
+      <c r="F2928">
+        <v>7378.32</v>
+      </c>
+      <c r="G2928">
+        <v>0</v>
+      </c>
+      <c r="H2928">
+        <v>0</v>
+      </c>
+      <c r="I2928">
+        <v>7378.32</v>
+      </c>
+      <c r="J2928">
+        <v>23785.06</v>
+      </c>
+      <c r="K2928" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B2929">
+        <v>14869.99</v>
+      </c>
+      <c r="C2929">
+        <v>60</v>
+      </c>
+      <c r="D2929">
+        <v>280</v>
+      </c>
+      <c r="E2929">
+        <v>14649.99</v>
+      </c>
+      <c r="F2929">
+        <v>150</v>
+      </c>
+      <c r="G2929">
+        <v>0</v>
+      </c>
+      <c r="H2929">
+        <v>0</v>
+      </c>
+      <c r="I2929">
+        <v>150</v>
+      </c>
+      <c r="J2929">
+        <v>14799.99</v>
+      </c>
+      <c r="K2929" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B2930">
+        <v>21980.6</v>
+      </c>
+      <c r="C2930">
+        <v>0</v>
+      </c>
+      <c r="D2930">
+        <v>0</v>
+      </c>
+      <c r="E2930">
+        <v>21980.6</v>
+      </c>
+      <c r="F2930">
+        <v>80</v>
+      </c>
+      <c r="G2930">
+        <v>0</v>
+      </c>
+      <c r="H2930">
+        <v>0</v>
+      </c>
+      <c r="I2930">
+        <v>80</v>
+      </c>
+      <c r="J2930">
+        <v>22060.6</v>
+      </c>
+      <c r="K2930" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B2931">
+        <v>10611.56</v>
+      </c>
+      <c r="C2931">
+        <v>0</v>
+      </c>
+      <c r="D2931">
+        <v>130</v>
+      </c>
+      <c r="E2931">
+        <v>10481.56</v>
+      </c>
+      <c r="F2931">
+        <v>0</v>
+      </c>
+      <c r="G2931">
+        <v>0</v>
+      </c>
+      <c r="H2931">
+        <v>0</v>
+      </c>
+      <c r="I2931">
+        <v>0</v>
+      </c>
+      <c r="J2931">
+        <v>10481.56</v>
+      </c>
+      <c r="K2931" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B2932">
+        <v>15739.25</v>
+      </c>
+      <c r="C2932">
+        <v>0</v>
+      </c>
+      <c r="D2932">
+        <v>0</v>
+      </c>
+      <c r="E2932">
+        <v>15739.25</v>
+      </c>
+      <c r="F2932">
+        <v>0</v>
+      </c>
+      <c r="G2932">
+        <v>0</v>
+      </c>
+      <c r="H2932">
+        <v>0</v>
+      </c>
+      <c r="I2932">
+        <v>0</v>
+      </c>
+      <c r="J2932">
+        <v>15739.25</v>
+      </c>
+      <c r="K2932" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="A2933" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B2933">
+        <v>12582.57</v>
+      </c>
+      <c r="C2933">
+        <v>2000</v>
+      </c>
+      <c r="D2933">
+        <v>0</v>
+      </c>
+      <c r="E2933">
+        <v>14582.57</v>
+      </c>
+      <c r="F2933">
+        <v>40</v>
+      </c>
+      <c r="G2933">
+        <v>0</v>
+      </c>
+      <c r="H2933">
+        <v>0</v>
+      </c>
+      <c r="I2933">
+        <v>40</v>
+      </c>
+      <c r="J2933">
+        <v>14622.57</v>
+      </c>
+      <c r="K2933" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B2934">
+        <v>17610.74</v>
+      </c>
+      <c r="C2934">
+        <v>0</v>
+      </c>
+      <c r="D2934">
+        <v>60</v>
+      </c>
+      <c r="E2934">
+        <v>17550.74</v>
+      </c>
+      <c r="F2934">
+        <v>14198</v>
+      </c>
+      <c r="G2934">
+        <v>0</v>
+      </c>
+      <c r="H2934">
+        <v>0</v>
+      </c>
+      <c r="I2934">
+        <v>14198</v>
+      </c>
+      <c r="J2934">
+        <v>31748.74</v>
+      </c>
+      <c r="K2934" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B2935">
+        <v>28003.37</v>
+      </c>
+      <c r="C2935">
+        <v>0</v>
+      </c>
+      <c r="D2935">
+        <v>1000</v>
+      </c>
+      <c r="E2935">
+        <v>27003.37</v>
+      </c>
+      <c r="F2935">
+        <v>420</v>
+      </c>
+      <c r="G2935">
+        <v>0</v>
+      </c>
+      <c r="H2935">
+        <v>0</v>
+      </c>
+      <c r="I2935">
+        <v>420</v>
+      </c>
+      <c r="J2935">
+        <v>27423.37</v>
+      </c>
+      <c r="K2935" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B2936">
+        <v>25271</v>
+      </c>
+      <c r="C2936">
+        <v>0</v>
+      </c>
+      <c r="D2936">
+        <v>0</v>
+      </c>
+      <c r="E2936">
+        <v>25271</v>
+      </c>
+      <c r="F2936">
+        <v>1785</v>
+      </c>
+      <c r="G2936">
+        <v>0</v>
+      </c>
+      <c r="H2936">
+        <v>0</v>
+      </c>
+      <c r="I2936">
+        <v>1785</v>
+      </c>
+      <c r="J2936">
+        <v>27056</v>
+      </c>
+      <c r="K2936" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B2937">
+        <v>26505.74</v>
+      </c>
+      <c r="C2937">
+        <v>2200</v>
+      </c>
+      <c r="D2937">
+        <v>300</v>
+      </c>
+      <c r="E2937">
+        <v>28405.74</v>
+      </c>
+      <c r="F2937">
+        <v>1010</v>
+      </c>
+      <c r="G2937">
+        <v>0</v>
+      </c>
+      <c r="H2937">
+        <v>0</v>
+      </c>
+      <c r="I2937">
+        <v>1010</v>
+      </c>
+      <c r="J2937">
+        <v>29415.74</v>
+      </c>
+      <c r="K2937" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B2938">
+        <v>10210</v>
+      </c>
+      <c r="C2938">
+        <v>0</v>
+      </c>
+      <c r="D2938">
+        <v>0</v>
+      </c>
+      <c r="E2938">
+        <v>10210</v>
+      </c>
+      <c r="F2938">
+        <v>0</v>
+      </c>
+      <c r="G2938">
+        <v>0</v>
+      </c>
+      <c r="H2938">
+        <v>0</v>
+      </c>
+      <c r="I2938">
+        <v>0</v>
+      </c>
+      <c r="J2938">
+        <v>10210</v>
+      </c>
+      <c r="K2938" t="inlineStr">
         <is>
           <t>CEBADA</t>
         </is>
